--- a/Website/static/downloads/integrations/supplier/SupplierOffers.xlsx
+++ b/Website/static/downloads/integrations/supplier/SupplierOffers.xlsx
@@ -118,7 +118,7 @@
   <cols>
     <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>

--- a/Website/static/downloads/integrations/supplier/SupplierOffers.xlsx
+++ b/Website/static/downloads/integrations/supplier/SupplierOffers.xlsx
@@ -118,7 +118,7 @@
   <cols>
     <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.17578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>

--- a/Website/static/downloads/integrations/supplier/SupplierOffers.xlsx
+++ b/Website/static/downloads/integrations/supplier/SupplierOffers.xlsx
@@ -16,7 +16,7 @@
     <x:t>Supplier offers / USD per unit</x:t>
   </x:si>
   <x:si>
-    <x:t>Editable numeric values; freight and tax excluded.</x:t>
+    <x:t>Freight and tax excluded. Compare delivery before ordering.</x:t>
   </x:si>
   <x:si>
     <x:t>Item</x:t>
@@ -52,7 +52,7 @@
     <x:numFmt numFmtId="165" formatCode="[h]:mm:ss"/>
     <x:numFmt numFmtId="166" formatCode="0.00"/>
   </x:numFmts>
-  <x:fonts count="3">
+  <x:fonts count="2">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Calibri"/>
@@ -61,11 +61,6 @@
       <x:b/>
       <x:sz val="11"/>
       <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
   <x:fills count="2">
@@ -82,10 +77,9 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="6">
+  <x:cellXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <x:xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -116,14 +110,14 @@
   <dimension ref="A1:D8"/>
   <x:sheetFormatPr xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="12.17578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
@@ -153,7 +147,7 @@
       <c r="B5" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="4" t="n">
         <v>89.50</v>
       </c>
       <c r="D5">
@@ -167,7 +161,7 @@
       <c r="B6" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="4" t="n">
         <v>92.00</v>
       </c>
       <c r="D6">
@@ -181,7 +175,7 @@
       <c r="B7" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="4" t="n">
         <v>215.00</v>
       </c>
       <c r="D7">
@@ -195,7 +189,7 @@
       <c r="B8" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="4" t="n">
         <v>208.00</v>
       </c>
       <c r="D8">

--- a/Website/static/downloads/integrations/supplier/SupplierOffers.xlsx
+++ b/Website/static/downloads/integrations/supplier/SupplierOffers.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:bookViews xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:bookViews>
     <x:workbookView/>
   </x:bookViews>
-  <sheets>
-    <sheet name="Offers" sheetId="1" r:id="rId1"/>
-  </sheets>
-</workbook>
+  <x:sheets>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offers" sheetId="1" r:id="R47a687fb0f23403f"/>
+  </x:sheets>
+</x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -55,12 +55,12 @@
   <x:fonts count="2">
     <x:font>
       <x:sz val="11"/>
-      <x:name val="Calibri"/>
+      <x:name val="Aptos"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:sz val="11"/>
-      <x:name val="Calibri"/>
+      <x:name val="Aptos"/>
     </x:font>
   </x:fonts>
   <x:fills count="2">
@@ -105,6 +105,289 @@
 </x:table>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="OfficeIMO Modern">
+  <a:themeElements>
+    <a:clrScheme name="Modern">
+      <a:dk1>
+        <a:srgbClr val="1B2433"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="5B6575"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="F6F8FB"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="3F64D7"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="DC7536"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="058E80"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="A52758"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="3F2F6B"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="255319"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="3F64D7"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="A52758"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Modern">
+      <a:majorFont>
+        <a:latin typeface="Aptos"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D8"/>
@@ -112,7 +395,7 @@
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="12.17578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.74609375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
   </cols>
   <sheetData>

--- a/Website/static/downloads/integrations/supplier/SupplierOffers.xlsx
+++ b/Website/static/downloads/integrations/supplier/SupplierOffers.xlsx
@@ -5,7 +5,7 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offers" sheetId="1" r:id="R47a687fb0f23403f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offers" sheetId="1" r:id="R5972a9fdaaea40c1"/>
   </x:sheets>
 </x:workbook>
 </file>
